--- a/docs/R2.2-experiment-blind/blind_discrimination.xlsx
+++ b/docs/R2.2-experiment-blind/blind_discrimination.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0Code\_phdSeismic\IEEE_Access\docs\R2.2-experiment-blind\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0E916E1-36B3-4EFC-BFA0-549623ED69E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{144F5AFF-F9FC-4FA2-B1A6-F72EDBCCEA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{7D8C605D-3345-4659-B0AA-FC2DD95A3C07}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="25365" windowHeight="21705" xr2:uid="{7D8C605D-3345-4659-B0AA-FC2DD95A3C07}"/>
   </bookViews>
   <sheets>
     <sheet name="blind_discrimination_experiment" sheetId="1" r:id="rId1"/>
@@ -7331,15 +7331,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF422F6D-2120-48E3-BB04-23E36AD4253D}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.5703125" customWidth="1"/>
+    <col min="2" max="2" width="53.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" customWidth="1"/>
     <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="3.42578125" customWidth="1"/>
     <col min="7" max="7" width="35.7109375" customWidth="1"/>
     <col min="8" max="8" width="63" customWidth="1"/>
     <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
@@ -7347,7 +7346,7 @@
     <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>184</v>
       </c>
@@ -7360,14 +7359,8 @@
       <c r="D1" t="s">
         <v>187</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>195</v>
       </c>
@@ -7380,14 +7373,8 @@
       <c r="D2" t="s">
         <v>198</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>206</v>
       </c>
@@ -7400,22 +7387,8 @@
       <c r="D3" t="s">
         <v>209</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="G4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>188</v>
       </c>
@@ -7425,14 +7398,8 @@
       <c r="D5" t="s">
         <v>190</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>199</v>
       </c>
@@ -7442,14 +7409,8 @@
       <c r="D6" t="s">
         <v>201</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>210</v>
       </c>
@@ -7459,22 +7420,8 @@
       <c r="D7" t="s">
         <v>212</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="G8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>191</v>
       </c>
@@ -7484,14 +7431,8 @@
       <c r="D9" t="s">
         <v>193</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>202</v>
       </c>
@@ -7501,14 +7442,8 @@
       <c r="D10" t="s">
         <v>204</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>213</v>
       </c>
@@ -7518,64 +7453,153 @@
       <c r="D11" t="s">
         <v>215</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="G12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="G13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D14" t="s">
         <v>194</v>
       </c>
-      <c r="G14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D15" t="s">
         <v>205</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D16" t="s">
         <v>216</v>
       </c>
-      <c r="G16" s="2" t="s">
+    </row>
+    <row r="19" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="33" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="33" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="33" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="33" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="33" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="B34" s="3" t="s">
         <v>229</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
